--- a/03_Outputs/Agua_Bosques_Turismo/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/02_Demografia/demografia.xlsx
@@ -112,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -181,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,19 +717,19 @@
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1396,29 +1534,29 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>Población total</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>Densidad poblacional (hab/km²)</t>
         </is>
@@ -1628,185 +1766,185 @@
   <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1831,91 +1969,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>2467</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>2522</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>763</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>667</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>624</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>729</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>605</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>568</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>516</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>345</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>172</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>389</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>351</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>320</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>356</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>304</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>267</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>242</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>168</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>70</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>374</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>316</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>304</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>373</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>301</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>301</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>274</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>177</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>102</v>
       </c>
     </row>
@@ -1938,91 +2076,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>8238</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>8448</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>2631</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>2376</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>2135</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>2273</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>2018</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>1841</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>1762</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>1122</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>528</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>1348</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>1170</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>1040</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>1110</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>978</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>871</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>889</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>577</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>255</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>1283</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>1206</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>1095</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>1163</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>1040</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>970</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>873</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>545</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>273</v>
       </c>
     </row>
@@ -2045,91 +2183,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>2628</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>2465</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>652</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>671</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>586</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>658</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>726</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>636</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>611</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>373</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>180</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>359</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>373</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>293</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>340</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>374</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>329</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>308</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>179</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>73</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>293</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>298</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>293</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>318</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>352</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>307</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>303</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>194</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>107</v>
       </c>
     </row>
@@ -2152,91 +2290,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>5372</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>5483</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>1929</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>1648</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>1414</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>1392</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>1287</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>1135</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>1109</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>655</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>286</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>1020</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>854</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>688</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>674</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>633</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>531</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>537</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>312</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>123</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>909</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>794</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>726</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>718</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>654</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>604</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>572</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>343</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>163</v>
       </c>
     </row>
@@ -2259,91 +2397,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>4405</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>4667</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>1120</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>1161</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>1331</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>1371</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>1245</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>1073</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>944</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>596</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>231</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>557</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>591</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>667</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>659</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>598</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>503</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>437</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>288</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>105</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>563</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>570</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>664</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>712</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>647</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>570</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>507</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>308</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>126</v>
       </c>
     </row>
@@ -2366,91 +2504,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="25">
         <v>34296</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <v>36096</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <v>9685</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="31">
         <v>9973</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>11504</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="35">
         <v>11614</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="37">
         <v>9633</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="39">
         <v>7449</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="41">
         <v>6087</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="43">
         <v>3248</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="45">
         <v>1199</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="47">
         <v>5049</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="49">
         <v>5039</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="51">
         <v>5742</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="53">
         <v>5788</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="55">
         <v>4623</v>
       </c>
-      <c r="U7" s="54">
+      <c r="U7" s="57">
         <v>3382</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="59">
         <v>2790</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="61">
         <v>1408</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="63">
         <v>475</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="65">
         <v>4636</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="Z7" s="67">
         <v>4934</v>
       </c>
-      <c r="AA7" s="66">
+      <c r="AA7" s="69">
         <v>5762</v>
       </c>
-      <c r="AB7" s="68">
+      <c r="AB7" s="71">
         <v>5826</v>
       </c>
-      <c r="AC7" s="70">
+      <c r="AC7" s="73">
         <v>5010</v>
       </c>
-      <c r="AD7" s="72">
+      <c r="AD7" s="75">
         <v>4067</v>
       </c>
-      <c r="AE7" s="74">
+      <c r="AE7" s="77">
         <v>3297</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="79">
         <v>1840</v>
       </c>
-      <c r="AG7" s="78">
+      <c r="AG7" s="81">
         <v>724</v>
       </c>
     </row>
@@ -2473,91 +2611,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <v>11082</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="27">
         <v>11654</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <v>3090</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="31">
         <v>3010</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="33">
         <v>3236</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="35">
         <v>3246</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="37">
         <v>3036</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="39">
         <v>2662</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="41">
         <v>2417</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="43">
         <v>1398</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="45">
         <v>641</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="47">
         <v>1532</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="49">
         <v>1528</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="51">
         <v>1590</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="53">
         <v>1581</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="55">
         <v>1521</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="57">
         <v>1269</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="59">
         <v>1148</v>
       </c>
-      <c r="W8" s="58">
+      <c r="W8" s="61">
         <v>642</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="63">
         <v>271</v>
       </c>
-      <c r="Y8" s="62">
+      <c r="Y8" s="65">
         <v>1558</v>
       </c>
-      <c r="Z8" s="64">
+      <c r="Z8" s="67">
         <v>1482</v>
       </c>
-      <c r="AA8" s="66">
+      <c r="AA8" s="69">
         <v>1646</v>
       </c>
-      <c r="AB8" s="68">
+      <c r="AB8" s="71">
         <v>1665</v>
       </c>
-      <c r="AC8" s="70">
+      <c r="AC8" s="73">
         <v>1515</v>
       </c>
-      <c r="AD8" s="72">
+      <c r="AD8" s="75">
         <v>1393</v>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="77">
         <v>1269</v>
       </c>
-      <c r="AF8" s="76">
+      <c r="AF8" s="79">
         <v>756</v>
       </c>
-      <c r="AG8" s="78">
+      <c r="AG8" s="81">
         <v>370</v>
       </c>
     </row>
@@ -2580,91 +2718,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="25">
         <v>8706</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="27">
         <v>8397</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <v>2543</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="31">
         <v>2544</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="33">
         <v>2193</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="35">
         <v>2468</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="37">
         <v>2106</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="39">
         <v>1925</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="41">
         <v>1818</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="43">
         <v>1023</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="45">
         <v>483</v>
       </c>
-      <c r="P9" s="44">
+      <c r="P9" s="47">
         <v>1291</v>
       </c>
-      <c r="Q9" s="46">
+      <c r="Q9" s="49">
         <v>1345</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="51">
         <v>1153</v>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="53">
         <v>1233</v>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="55">
         <v>1061</v>
       </c>
-      <c r="U9" s="54">
+      <c r="U9" s="57">
         <v>960</v>
       </c>
-      <c r="V9" s="56">
+      <c r="V9" s="59">
         <v>915</v>
       </c>
-      <c r="W9" s="58">
+      <c r="W9" s="61">
         <v>528</v>
       </c>
-      <c r="X9" s="60">
+      <c r="X9" s="63">
         <v>220</v>
       </c>
-      <c r="Y9" s="62">
+      <c r="Y9" s="65">
         <v>1252</v>
       </c>
-      <c r="Z9" s="64">
+      <c r="Z9" s="67">
         <v>1199</v>
       </c>
-      <c r="AA9" s="66">
+      <c r="AA9" s="69">
         <v>1040</v>
       </c>
-      <c r="AB9" s="68">
+      <c r="AB9" s="71">
         <v>1235</v>
       </c>
-      <c r="AC9" s="70">
+      <c r="AC9" s="73">
         <v>1045</v>
       </c>
-      <c r="AD9" s="72">
+      <c r="AD9" s="75">
         <v>965</v>
       </c>
-      <c r="AE9" s="74">
+      <c r="AE9" s="77">
         <v>903</v>
       </c>
-      <c r="AF9" s="76">
+      <c r="AF9" s="79">
         <v>495</v>
       </c>
-      <c r="AG9" s="78">
+      <c r="AG9" s="81">
         <v>263</v>
       </c>
     </row>
@@ -2687,91 +2825,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <v>2999</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="27">
         <v>3049</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <v>1116</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="31">
         <v>972</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="33">
         <v>778</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="35">
         <v>797</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="37">
         <v>693</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="39">
         <v>536</v>
       </c>
-      <c r="M10" s="38">
+      <c r="M10" s="41">
         <v>573</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="43">
         <v>406</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="45">
         <v>177</v>
       </c>
-      <c r="P10" s="44">
+      <c r="P10" s="47">
         <v>566</v>
       </c>
-      <c r="Q10" s="46">
+      <c r="Q10" s="49">
         <v>488</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R10" s="51">
         <v>377</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="53">
         <v>369</v>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="55">
         <v>354</v>
       </c>
-      <c r="U10" s="54">
+      <c r="U10" s="57">
         <v>258</v>
       </c>
-      <c r="V10" s="56">
+      <c r="V10" s="59">
         <v>283</v>
       </c>
-      <c r="W10" s="58">
+      <c r="W10" s="61">
         <v>213</v>
       </c>
-      <c r="X10" s="60">
+      <c r="X10" s="63">
         <v>91</v>
       </c>
-      <c r="Y10" s="62">
+      <c r="Y10" s="65">
         <v>550</v>
       </c>
-      <c r="Z10" s="64">
+      <c r="Z10" s="67">
         <v>484</v>
       </c>
-      <c r="AA10" s="66">
+      <c r="AA10" s="69">
         <v>401</v>
       </c>
-      <c r="AB10" s="68">
+      <c r="AB10" s="71">
         <v>428</v>
       </c>
-      <c r="AC10" s="70">
+      <c r="AC10" s="73">
         <v>339</v>
       </c>
-      <c r="AD10" s="72">
+      <c r="AD10" s="75">
         <v>278</v>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="77">
         <v>290</v>
       </c>
-      <c r="AF10" s="76">
+      <c r="AF10" s="79">
         <v>193</v>
       </c>
-      <c r="AG10" s="78">
+      <c r="AG10" s="81">
         <v>86</v>
       </c>
     </row>
@@ -2794,91 +2932,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="25">
         <v>6787</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="27">
         <v>7106</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <v>2546</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="31">
         <v>2236</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="33">
         <v>1923</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="35">
         <v>2114</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="37">
         <v>1739</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="39">
         <v>1254</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="41">
         <v>1051</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="43">
         <v>695</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="45">
         <v>335</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="47">
         <v>1289</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="49">
         <v>1148</v>
       </c>
-      <c r="R11" s="48">
+      <c r="R11" s="51">
         <v>942</v>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="53">
         <v>1015</v>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="55">
         <v>827</v>
       </c>
-      <c r="U11" s="54">
+      <c r="U11" s="57">
         <v>632</v>
       </c>
-      <c r="V11" s="56">
+      <c r="V11" s="59">
         <v>488</v>
       </c>
-      <c r="W11" s="58">
+      <c r="W11" s="61">
         <v>299</v>
       </c>
-      <c r="X11" s="60">
+      <c r="X11" s="63">
         <v>147</v>
       </c>
-      <c r="Y11" s="62">
+      <c r="Y11" s="65">
         <v>1257</v>
       </c>
-      <c r="Z11" s="64">
+      <c r="Z11" s="67">
         <v>1088</v>
       </c>
-      <c r="AA11" s="66">
+      <c r="AA11" s="69">
         <v>981</v>
       </c>
-      <c r="AB11" s="68">
+      <c r="AB11" s="71">
         <v>1099</v>
       </c>
-      <c r="AC11" s="70">
+      <c r="AC11" s="73">
         <v>912</v>
       </c>
-      <c r="AD11" s="72">
+      <c r="AD11" s="75">
         <v>622</v>
       </c>
-      <c r="AE11" s="74">
+      <c r="AE11" s="77">
         <v>563</v>
       </c>
-      <c r="AF11" s="76">
+      <c r="AF11" s="79">
         <v>396</v>
       </c>
-      <c r="AG11" s="78">
+      <c r="AG11" s="81">
         <v>188</v>
       </c>
     </row>
@@ -2901,91 +3039,91 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="25">
         <v>8345</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="27">
         <v>8408</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <v>2307</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="31">
         <v>2356</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="33">
         <v>2276</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="35">
         <v>2520</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="37">
         <v>2055</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="39">
         <v>1863</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12" s="41">
         <v>1791</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="43">
         <v>1049</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="45">
         <v>536</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="47">
         <v>1212</v>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="49">
         <v>1239</v>
       </c>
-      <c r="R12" s="48">
+      <c r="R12" s="51">
         <v>1118</v>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="53">
         <v>1265</v>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="55">
         <v>996</v>
       </c>
-      <c r="U12" s="54">
+      <c r="U12" s="57">
         <v>914</v>
       </c>
-      <c r="V12" s="56">
+      <c r="V12" s="59">
         <v>877</v>
       </c>
-      <c r="W12" s="58">
+      <c r="W12" s="61">
         <v>485</v>
       </c>
-      <c r="X12" s="60">
+      <c r="X12" s="63">
         <v>239</v>
       </c>
-      <c r="Y12" s="62">
+      <c r="Y12" s="65">
         <v>1095</v>
       </c>
-      <c r="Z12" s="64">
+      <c r="Z12" s="67">
         <v>1117</v>
       </c>
-      <c r="AA12" s="66">
+      <c r="AA12" s="69">
         <v>1158</v>
       </c>
-      <c r="AB12" s="68">
+      <c r="AB12" s="71">
         <v>1255</v>
       </c>
-      <c r="AC12" s="70">
+      <c r="AC12" s="73">
         <v>1059</v>
       </c>
-      <c r="AD12" s="72">
+      <c r="AD12" s="75">
         <v>949</v>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="77">
         <v>914</v>
       </c>
-      <c r="AF12" s="76">
+      <c r="AF12" s="79">
         <v>564</v>
       </c>
-      <c r="AG12" s="78">
+      <c r="AG12" s="81">
         <v>297</v>
       </c>
     </row>
@@ -3008,200 +3146,200 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="25">
         <v>12358</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="27">
         <v>11356</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="29">
         <v>3161</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="31">
         <v>3307</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="33">
         <v>3460</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="35">
         <v>3531</v>
       </c>
-      <c r="K13" s="34">
+      <c r="K13" s="37">
         <v>3349</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="39">
         <v>2578</v>
       </c>
-      <c r="M13" s="38">
+      <c r="M13" s="41">
         <v>2385</v>
       </c>
-      <c r="N13" s="40">
+      <c r="N13" s="43">
         <v>1360</v>
       </c>
-      <c r="O13" s="42">
+      <c r="O13" s="45">
         <v>583</v>
       </c>
-      <c r="P13" s="44">
+      <c r="P13" s="47">
         <v>1623</v>
       </c>
-      <c r="Q13" s="46">
+      <c r="Q13" s="49">
         <v>1804</v>
       </c>
-      <c r="R13" s="48">
+      <c r="R13" s="51">
         <v>1855</v>
       </c>
-      <c r="S13" s="50">
+      <c r="S13" s="53">
         <v>1882</v>
       </c>
-      <c r="T13" s="52">
+      <c r="T13" s="55">
         <v>1775</v>
       </c>
-      <c r="U13" s="54">
+      <c r="U13" s="57">
         <v>1303</v>
       </c>
-      <c r="V13" s="56">
+      <c r="V13" s="59">
         <v>1182</v>
       </c>
-      <c r="W13" s="58">
+      <c r="W13" s="61">
         <v>653</v>
       </c>
-      <c r="X13" s="60">
+      <c r="X13" s="63">
         <v>281</v>
       </c>
-      <c r="Y13" s="62">
+      <c r="Y13" s="65">
         <v>1538</v>
       </c>
-      <c r="Z13" s="64">
+      <c r="Z13" s="67">
         <v>1503</v>
       </c>
-      <c r="AA13" s="66">
+      <c r="AA13" s="69">
         <v>1605</v>
       </c>
-      <c r="AB13" s="68">
+      <c r="AB13" s="71">
         <v>1649</v>
       </c>
-      <c r="AC13" s="70">
+      <c r="AC13" s="73">
         <v>1574</v>
       </c>
-      <c r="AD13" s="72">
+      <c r="AD13" s="75">
         <v>1275</v>
       </c>
-      <c r="AE13" s="74">
+      <c r="AE13" s="77">
         <v>1203</v>
       </c>
-      <c r="AF13" s="76">
+      <c r="AF13" s="79">
         <v>707</v>
       </c>
-      <c r="AG13" s="78">
+      <c r="AG13" s="81">
         <v>302</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="26">
         <v>107683</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="28">
         <v>109651</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="30">
         <v>31543</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="32">
         <v>30921</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="34">
         <v>31460</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="36">
         <v>32713</v>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="38">
         <v>28492</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="40">
         <v>23520</v>
       </c>
-      <c r="M14" s="39">
+      <c r="M14" s="42">
         <v>21064</v>
       </c>
-      <c r="N14" s="41">
+      <c r="N14" s="44">
         <v>12270</v>
       </c>
-      <c r="O14" s="43">
+      <c r="O14" s="46">
         <v>5351</v>
       </c>
-      <c r="P14" s="45">
+      <c r="P14" s="48">
         <v>16235</v>
       </c>
-      <c r="Q14" s="47">
+      <c r="Q14" s="50">
         <v>15930</v>
       </c>
-      <c r="R14" s="49">
+      <c r="R14" s="52">
         <v>15785</v>
       </c>
-      <c r="S14" s="51">
+      <c r="S14" s="54">
         <v>16272</v>
       </c>
-      <c r="T14" s="53">
+      <c r="T14" s="56">
         <v>14044</v>
       </c>
-      <c r="U14" s="55">
+      <c r="U14" s="58">
         <v>11219</v>
       </c>
-      <c r="V14" s="57">
+      <c r="V14" s="60">
         <v>10096</v>
       </c>
-      <c r="W14" s="59">
+      <c r="W14" s="62">
         <v>5752</v>
       </c>
-      <c r="X14" s="61">
+      <c r="X14" s="64">
         <v>2350</v>
       </c>
-      <c r="Y14" s="63">
+      <c r="Y14" s="66">
         <v>15308</v>
       </c>
-      <c r="Z14" s="65">
+      <c r="Z14" s="68">
         <v>14991</v>
       </c>
-      <c r="AA14" s="67">
+      <c r="AA14" s="70">
         <v>15675</v>
       </c>
-      <c r="AB14" s="69">
+      <c r="AB14" s="72">
         <v>16441</v>
       </c>
-      <c r="AC14" s="71">
+      <c r="AC14" s="74">
         <v>14448</v>
       </c>
-      <c r="AD14" s="73">
+      <c r="AD14" s="76">
         <v>12301</v>
       </c>
-      <c r="AE14" s="75">
+      <c r="AE14" s="78">
         <v>10968</v>
       </c>
-      <c r="AF14" s="77">
+      <c r="AF14" s="80">
         <v>6518</v>
       </c>
-      <c r="AG14" s="79">
+      <c r="AG14" s="82">
         <v>3001</v>
       </c>
     </row>
@@ -3217,47 +3355,47 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="68.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="69.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -3282,14 +3420,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>5.45808966861598</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>5.58121632024634</v>
       </c>
-      <c r="G2" s="84">
-        <v>34.9206349206349</v>
+      <c r="G2" s="90">
+        <v>32.8214111328125</v>
       </c>
     </row>
     <row r="3">
@@ -3311,14 +3449,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>11.1382266441399</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>5.6655460092143</v>
       </c>
-      <c r="G3" s="84">
-        <v>33.8138385502471</v>
+      <c r="G3" s="90">
+        <v>34.8453598022461</v>
       </c>
     </row>
     <row r="4">
@@ -3340,14 +3478,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>3.16706254948535</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>4.69851213782302</v>
       </c>
-      <c r="G4" s="84">
-        <v>38.4579870729455</v>
+      <c r="G4" s="90">
+        <v>39.2475624084473</v>
       </c>
     </row>
     <row r="5">
@@ -3369,14 +3507,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>10.5343803868991</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>4.30086973143458</v>
       </c>
-      <c r="G5" s="84">
-        <v>29.9773522750669</v>
+      <c r="G5" s="90">
+        <v>27.7305564880371</v>
       </c>
     </row>
     <row r="6">
@@ -3398,14 +3536,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>8.9666951323655</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>5.56839672200042</v>
       </c>
-      <c r="G6" s="84">
-        <v>36.1934926576447</v>
+      <c r="G6" s="90">
+        <v>34.3800315856934</v>
       </c>
     </row>
     <row r="7">
@@ -3427,14 +3565,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="86">
         <v>10.625147571494</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="88">
         <v>4.67884260209317</v>
       </c>
-      <c r="G7" s="84">
-        <v>28.3453923829212</v>
+      <c r="G7" s="90">
+        <v>28.5380878448486</v>
       </c>
     </row>
     <row r="8">
@@ -3456,14 +3594,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="86">
         <v>9.11565213634596</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="88">
         <v>5.78945127921332</v>
       </c>
-      <c r="G8" s="84">
-        <v>34.5484581497797</v>
+      <c r="G8" s="90">
+        <v>34.4879188537598</v>
       </c>
     </row>
     <row r="9">
@@ -3485,14 +3623,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="86">
         <v>6.18054317465977</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="88">
         <v>5.08514664143803</v>
       </c>
-      <c r="G9" s="84">
-        <v>32.35253296322</v>
+      <c r="G9" s="90">
+        <v>29.8723163604736</v>
       </c>
     </row>
     <row r="10">
@@ -3514,14 +3652,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="86">
         <v>7.5503355704698</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="88">
         <v>8.3153168135706</v>
       </c>
-      <c r="G10" s="84">
-        <v>30.5060584461867</v>
+      <c r="G10" s="90">
+        <v>30.8986759185791</v>
       </c>
     </row>
     <row r="11">
@@ -3543,14 +3681,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="86">
         <v>10.3796388454429</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="88">
         <v>5.61718859710715</v>
       </c>
-      <c r="G11" s="84">
-        <v>25.7279890373416</v>
+      <c r="G11" s="90">
+        <v>26.474027633667</v>
       </c>
     </row>
     <row r="12">
@@ -3572,14 +3710,14 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="86">
         <v>8.42068072076316</v>
       </c>
-      <c r="F12" s="82">
+      <c r="F12" s="88">
         <v>5.34200441296017</v>
       </c>
-      <c r="G12" s="84">
-        <v>34.7321039639901</v>
+      <c r="G12" s="90">
+        <v>32.3455390930176</v>
       </c>
     </row>
     <row r="13">
@@ -3601,107 +3739,107 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="86">
         <v>6.80046442196052</v>
       </c>
-      <c r="F13" s="82">
+      <c r="F13" s="88">
         <v>4.15749572022499</v>
       </c>
-      <c r="G13" s="84">
-        <v>32.9581466506393</v>
+      <c r="G13" s="90">
+        <v>32.490779876709</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por población)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="87">
         <v>9.10747221242821</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="89">
         <v>5.0928283119626</v>
       </c>
-      <c r="G14" s="85">
-        <v>31.3920887384398</v>
+      <c r="G14" s="91">
+        <v>30.9433794010351</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN ORIENTE (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="87">
         <v>8.83388284969214</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="89">
         <v>5.38854798755923</v>
       </c>
-      <c r="G15" s="85">
-        <v>32.7273397959139</v>
+      <c r="G15" s="91">
+        <v>31.474378317769</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G16" s="85">
-        <v>32.052654940463</v>
+      <c r="G16" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -3716,47 +3854,47 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="68.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="69.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -3781,13 +3919,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>1.81144652116102</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>0</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>4.39181900885634</v>
       </c>
     </row>
@@ -3810,13 +3948,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>1.72526243331612</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>1.59316411743596</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>1.84911534066281</v>
       </c>
     </row>
@@ -3839,13 +3977,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>0</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>0</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3868,13 +4006,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>3.47648824695554</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>4.65502967822555</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>1.84772929652716</v>
       </c>
     </row>
@@ -3897,13 +4035,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>10.3083292398552</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>13.3014206198107</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>3.85094324822528</v>
       </c>
     </row>
@@ -3926,13 +4064,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="95">
         <v>2.42498428717658</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="97">
         <v>2.85224670925089</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="99">
         <v>1.28182064469566</v>
       </c>
     </row>
@@ -3955,13 +4093,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="95">
         <v>3.53315671387961</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="97">
         <v>1.87882101496098</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="99">
         <v>5.73784703898163</v>
       </c>
     </row>
@@ -3984,13 +4122,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="95">
         <v>0.664523696400996</v>
       </c>
-      <c r="F9" s="88">
+      <c r="F9" s="97">
         <v>0.54768943050193</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="99">
         <v>0.777777777777779</v>
       </c>
     </row>
@@ -4013,13 +4151,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="95">
         <v>3.84842538080553</v>
       </c>
-      <c r="F10" s="88">
+      <c r="F10" s="97">
         <v>2.7112188365651</v>
       </c>
-      <c r="G10" s="90">
+      <c r="G10" s="99">
         <v>4.92276378439283</v>
       </c>
     </row>
@@ -4042,13 +4180,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="95">
         <v>2.17472045850424</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="97">
         <v>0.332984049365469</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="99">
         <v>5.27581318896747</v>
       </c>
     </row>
@@ -4071,13 +4209,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="95">
         <v>1.42992223524172</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="97">
         <v>0.452644939709561</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="99">
         <v>2.58416945373467</v>
       </c>
     </row>
@@ -4100,106 +4238,106 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="95">
         <v>1.81124745660607</v>
       </c>
-      <c r="F13" s="88">
+      <c r="F13" s="97">
         <v>2.3091942005618</v>
       </c>
-      <c r="G13" s="90">
+      <c r="G13" s="99">
         <v>1.58848018341437</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por población)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="96">
         <v>2.55701887447622</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="98">
         <v>2.47649429619045</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="100">
         <v>2.42876654965022</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN ORIENTE (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="96">
         <v>2.815721325682</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="98">
         <v>2.51738375125153</v>
       </c>
-      <c r="G15" s="91">
+      <c r="G15" s="100">
         <v>3.12437884704046</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="87">
+      <c r="E16" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F16" s="89">
+      <c r="F16" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G16" s="91">
+      <c r="G16" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -4215,23 +4353,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -4405,35 +4543,35 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -4679,22 +4817,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -4868,23 +5007,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -5172,17 +5311,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -5195,7 +5334,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>34.9206349206349</v>
+        <v>32.8214111328125</v>
       </c>
     </row>
     <row r="3">
@@ -5205,7 +5344,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>33.8138385502471</v>
+        <v>34.8453598022461</v>
       </c>
     </row>
     <row r="4">
@@ -5215,7 +5354,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>38.4579870729455</v>
+        <v>39.2475624084473</v>
       </c>
     </row>
     <row r="5">
@@ -5225,7 +5364,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>29.9773522750669</v>
+        <v>27.7305564880371</v>
       </c>
     </row>
     <row r="6">
@@ -5235,7 +5374,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>36.1934926576447</v>
+        <v>34.3800315856934</v>
       </c>
     </row>
     <row r="7">
@@ -5245,7 +5384,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>28.3453923829212</v>
+        <v>28.5380878448486</v>
       </c>
     </row>
     <row r="8">
@@ -5255,7 +5394,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>34.5484581497797</v>
+        <v>34.4879188537598</v>
       </c>
     </row>
     <row r="9">
@@ -5265,7 +5404,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>32.35253296322</v>
+        <v>29.8723163604736</v>
       </c>
     </row>
     <row r="10">
@@ -5275,7 +5414,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>30.5060584461867</v>
+        <v>30.8986759185791</v>
       </c>
     </row>
     <row r="11">
@@ -5285,7 +5424,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>25.7279890373416</v>
+        <v>26.474027633667</v>
       </c>
     </row>
     <row r="12">
@@ -5295,7 +5434,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>34.7321039639901</v>
+        <v>32.3455390930176</v>
       </c>
     </row>
     <row r="13">
@@ -5305,7 +5444,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>32.9581466506393</v>
+        <v>32.490779876709</v>
       </c>
     </row>
   </sheetData>
